--- a/nr-update-headcircum/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-update-headcircum/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-10T12:31:30+00:00</t>
+    <t>2025-07-21T09:29:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
